--- a/data/trans_orig/P05A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124004</t>
+          <t>123629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163784</t>
+          <t>166366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137795</t>
+          <t>136721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177895</t>
+          <t>174116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271617</t>
+          <t>272599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330576</t>
+          <t>331328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330280</t>
+          <t>327698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>370060</t>
+          <t>370435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289594</t>
+          <t>293373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329694</t>
+          <t>330768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630977</t>
+          <t>630225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689936</t>
+          <t>688954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180309</t>
+          <t>182245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231407</t>
+          <t>233342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>176001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225109</t>
+          <t>224401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>369959</t>
+          <t>371131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442277</t>
+          <t>438471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504082</t>
+          <t>502147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>555180</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400385</t>
+          <t>401093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449137</t>
+          <t>449493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>918705</t>
+          <t>922511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>991023</t>
+          <t>989851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167670</t>
+          <t>166977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216690</t>
+          <t>213493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>234257</t>
+          <t>234303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285402</t>
+          <t>289119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>416176</t>
+          <t>417454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487985</t>
+          <t>486749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421978</t>
+          <t>425175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470998</t>
+          <t>471691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>404342</t>
+          <t>400625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455487</t>
+          <t>455441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>840427</t>
+          <t>841663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>912236</t>
+          <t>910958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148578</t>
+          <t>146639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194666</t>
+          <t>188885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162958</t>
+          <t>163110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205616</t>
+          <t>205237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321730</t>
+          <t>323865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387490</t>
+          <t>385099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324481</t>
+          <t>330262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370569</t>
+          <t>372508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310026</t>
+          <t>310405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352684</t>
+          <t>352532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>647299</t>
+          <t>649690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713059</t>
+          <t>710924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101403</t>
+          <t>100256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134111</t>
+          <t>134965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128032</t>
+          <t>126573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167644</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238827</t>
+          <t>238430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291479</t>
+          <t>291938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>252599</t>
+          <t>251745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285307</t>
+          <t>286454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236342</t>
+          <t>235810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>275954</t>
+          <t>277413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>499217</t>
+          <t>498758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>551869</t>
+          <t>552266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67342</t>
+          <t>66712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95522</t>
+          <t>95034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>99708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>133601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177712</t>
+          <t>176834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220977</t>
+          <t>220743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197061</t>
+          <t>197549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225241</t>
+          <t>225871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209635</t>
+          <t>209333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242995</t>
+          <t>243226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414540</t>
+          <t>414774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>457805</t>
+          <t>458683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73162</t>
+          <t>72821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80248</t>
+          <t>82226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117577</t>
+          <t>115983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135091</t>
+          <t>136282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178325</t>
+          <t>181126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136721</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162861</t>
+          <t>162050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216331</t>
+          <t>217925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253660</t>
+          <t>251682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>365466</t>
+          <t>362665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>408700</t>
+          <t>407509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>919208</t>
+          <t>920308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1028197</t>
+          <t>1021510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1107855</t>
+          <t>1111094</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1219558</t>
+          <t>1220849</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2057115</t>
+          <t>2048095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2216172</t>
+          <t>2207510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2248346</t>
+          <t>2255033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2357335</t>
+          <t>2356235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2159639</t>
+          <t>2158348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2271342</t>
+          <t>2268103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4439569</t>
+          <t>4448231</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4598626</t>
+          <t>4607646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144472</t>
+          <t>142546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183598</t>
+          <t>183817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137537</t>
+          <t>137641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178860</t>
+          <t>179000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>293742</t>
+          <t>292307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>348015</t>
+          <t>349533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269596</t>
+          <t>269377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308722</t>
+          <t>310648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250356</t>
+          <t>250216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291679</t>
+          <t>291575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534395</t>
+          <t>532877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588668</t>
+          <t>590103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245197</t>
+          <t>247188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298012</t>
+          <t>299609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206655</t>
+          <t>209236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257886</t>
+          <t>258035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>466270</t>
+          <t>464342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540022</t>
+          <t>539696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387532</t>
+          <t>385935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440347</t>
+          <t>438356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352369</t>
+          <t>352220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403600</t>
+          <t>401019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>755777</t>
+          <t>756103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>829529</t>
+          <t>831457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,17%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>234140</t>
+          <t>235071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>288327</t>
+          <t>288696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>260499</t>
+          <t>261475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>313021</t>
+          <t>314280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512690</t>
+          <t>511309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>583180</t>
+          <t>583904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>392809</t>
+          <t>392440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446996</t>
+          <t>446065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>396110</t>
+          <t>394851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448632</t>
+          <t>447656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>807086</t>
+          <t>806362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877576</t>
+          <t>878957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219736</t>
+          <t>221252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243692</t>
+          <t>244070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293122</t>
+          <t>295925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>478954</t>
+          <t>479069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>555146</t>
+          <t>553336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342840</t>
+          <t>339909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>393857</t>
+          <t>392341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322016</t>
+          <t>319213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371446</t>
+          <t>371068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673585</t>
+          <t>675395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749777</t>
+          <t>749662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>165689</t>
+          <t>166904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208813</t>
+          <t>210221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153165</t>
+          <t>153572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196346</t>
+          <t>196799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>332215</t>
+          <t>330520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393832</t>
+          <t>393571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220616</t>
+          <t>219208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263740</t>
+          <t>262525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249396</t>
+          <t>248943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292577</t>
+          <t>292170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>481339</t>
+          <t>481600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>542956</t>
+          <t>544651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118532</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153131</t>
+          <t>155986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123256</t>
+          <t>122937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159003</t>
+          <t>161558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>252422</t>
+          <t>250846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>306714</t>
+          <t>304441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156655</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191254</t>
+          <t>192067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194993</t>
+          <t>192438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230740</t>
+          <t>231059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357068</t>
+          <t>359341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>411360</t>
+          <t>412936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77143</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>108512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>130671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171821</t>
+          <t>172050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218313</t>
+          <t>218181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268316</t>
+          <t>270811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138232</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>171540</t>
+          <t>172876</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217158</t>
+          <t>216929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256696</t>
+          <t>258308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>369346</t>
+          <t>366851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>419349</t>
+          <t>419481</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1300708</t>
+          <t>1298317</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1414412</t>
+          <t>1417843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1359477</t>
+          <t>1359339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1478927</t>
+          <t>1479418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2690560</t>
+          <t>2683574</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2866196</t>
+          <t>2858180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2006953</t>
+          <t>2003522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2120657</t>
+          <t>2123048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2073531</t>
+          <t>2073040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2192981</t>
+          <t>2193119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4107627</t>
+          <t>4115643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4283263</t>
+          <t>4290249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129153</t>
+          <t>128269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166985</t>
+          <t>168086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115777</t>
+          <t>116282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152562</t>
+          <t>153212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253371</t>
+          <t>256765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308038</t>
+          <t>307032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252478</t>
+          <t>251377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290310</t>
+          <t>291194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243193</t>
+          <t>242543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>279473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507180</t>
+          <t>508186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561847</t>
+          <t>558453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195145</t>
+          <t>194486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241790</t>
+          <t>242220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194928</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239493</t>
+          <t>239680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>402427</t>
+          <t>404252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>464730</t>
+          <t>466963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348706</t>
+          <t>348276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395351</t>
+          <t>396010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324051</t>
+          <t>323864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368616</t>
+          <t>370077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>687077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751613</t>
+          <t>749788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197825</t>
+          <t>198399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245231</t>
+          <t>248142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225128</t>
+          <t>222296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272325</t>
+          <t>273157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437257</t>
+          <t>434026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>510661</t>
+          <t>506546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>420955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471272</t>
+          <t>470698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389061</t>
+          <t>388229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>436258</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>819822</t>
+          <t>823937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>893226</t>
+          <t>896457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225846</t>
+          <t>224863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278566</t>
+          <t>276436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234547</t>
+          <t>231105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286674</t>
+          <t>283358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>471024</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>543814</t>
+          <t>543281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366215</t>
+          <t>368345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>418935</t>
+          <t>419918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362403</t>
+          <t>365719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414530</t>
+          <t>417972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>750044</t>
+          <t>750577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>822834</t>
+          <t>820133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154922</t>
+          <t>153566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199212</t>
+          <t>199083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160455</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205883</t>
+          <t>208069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>329748</t>
+          <t>328842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>391641</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>278706</t>
+          <t>278835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322996</t>
+          <t>324352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>290966</t>
+          <t>288780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>336394</t>
+          <t>332755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>583126</t>
+          <t>579758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>645019</t>
+          <t>645925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111415</t>
+          <t>110723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147032</t>
+          <t>146154</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117030</t>
+          <t>119874</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>156878</t>
+          <t>159419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238564</t>
+          <t>238181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>292656</t>
+          <t>293025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187298</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222915</t>
+          <t>223607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219849</t>
+          <t>217308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>256853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418401</t>
+          <t>418032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472493</t>
+          <t>472876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>62471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>91156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>98215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>140252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169615</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>221013</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168073</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196390</t>
+          <t>194527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257506</t>
+          <t>258646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300251</t>
+          <t>300683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>434883</t>
+          <t>437420</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>486281</t>
+          <t>485712</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1165437</t>
+          <t>1164617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1276521</t>
+          <t>1275558</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1235034</t>
+          <t>1236745</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1354433</t>
+          <t>1356620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2438907</t>
+          <t>2437893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2595963</t>
+          <t>2595935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2116562</t>
+          <t>2117525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2227646</t>
+          <t>2228466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2187803</t>
+          <t>2185616</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2307202</t>
+          <t>2305491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4339356</t>
+          <t>4339384</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4496412</t>
+          <t>4497426</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>73962</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>50514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>100699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59806</t>
+          <t>69060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100130</t>
+          <t>115847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>148248</t>
+          <t>164374</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117696</t>
+          <t>133907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182505</t>
+          <t>202556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>329833</t>
+          <t>333831</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301713</t>
+          <t>307094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>352128</t>
+          <t>357279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>235105</t>
+          <t>272099</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213070</t>
+          <t>246665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253394</t>
+          <t>293452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>564939</t>
+          <t>605931</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>530682</t>
+          <t>567749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595491</t>
+          <t>636398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74094</t>
+          <t>87878</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95926</t>
+          <t>111854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90479</t>
+          <t>101719</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57630</t>
+          <t>83264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114121</t>
+          <t>121724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>164573</t>
+          <t>189598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123462</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193608</t>
+          <t>222213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>349453</t>
+          <t>389012</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>327621</t>
+          <t>365036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>408552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>421614</t>
+          <t>400014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397972</t>
+          <t>380009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454463</t>
+          <t>418469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>771067</t>
+          <t>789025</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742032</t>
+          <t>756410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>812178</t>
+          <t>816643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>113343</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93387</t>
+          <t>109343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133407</t>
+          <t>152974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>107179</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78698</t>
+          <t>111849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125132</t>
+          <t>146083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>220522</t>
+          <t>259126</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186592</t>
+          <t>233944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249026</t>
+          <t>287025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422667</t>
+          <t>487915</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402603</t>
+          <t>465567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>442623</t>
+          <t>509198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>484093</t>
+          <t>493946</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466140</t>
+          <t>476363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512574</t>
+          <t>510597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>906760</t>
+          <t>981861</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>878256</t>
+          <t>953962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>940690</t>
+          <t>1007043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1127282</t>
+          <t>1240987</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1127282</t>
+          <t>1240987</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1127282</t>
+          <t>1240987</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>139403</t>
+          <t>146618</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>124450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202778</t>
+          <t>170917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>144886</t>
+          <t>158601</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120933</t>
+          <t>142716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163870</t>
+          <t>176961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>284290</t>
+          <t>305219</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179368</t>
+          <t>275180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>350399</t>
+          <t>331200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>748383</t>
+          <t>553999</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>685008</t>
+          <t>529700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>828277</t>
+          <t>576167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>567995</t>
+          <t>578285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>549011</t>
+          <t>559925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591948</t>
+          <t>594170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1316377</t>
+          <t>1132285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1250268</t>
+          <t>1106304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1421299</t>
+          <t>1162324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91966</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>83077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110158</t>
+          <t>116371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>114233</t>
+          <t>128716</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>113466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129533</t>
+          <t>147663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>206199</t>
+          <t>227171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185964</t>
+          <t>205448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227845</t>
+          <t>251232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>469268</t>
+          <t>510892</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451076</t>
+          <t>492975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>483207</t>
+          <t>526269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>433060</t>
+          <t>479454</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417760</t>
+          <t>460507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445607</t>
+          <t>494704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>902327</t>
+          <t>990346</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>880681</t>
+          <t>966285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>922562</t>
+          <t>1012069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64635</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76873</t>
+          <t>86385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>273695</t>
+          <t>79012</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99548</t>
+          <t>67941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>455235</t>
+          <t>93353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>338330</t>
+          <t>151371</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163723</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>634721</t>
+          <t>169379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>303530</t>
+          <t>334720</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291292</t>
+          <t>320695</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314541</t>
+          <t>346599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>334673</t>
+          <t>360154</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>345813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>508820</t>
+          <t>371225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>638203</t>
+          <t>694875</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341812</t>
+          <t>676867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>711403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>56968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56797</t>
+          <t>62472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78249</t>
+          <t>86861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>107523</t>
+          <t>119441</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94026</t>
+          <t>104807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122592</t>
+          <t>136694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>241754</t>
+          <t>265102</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232163</t>
+          <t>253230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251387</t>
+          <t>275190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>359313</t>
+          <t>390264</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>347582</t>
+          <t>377748</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>369034</t>
+          <t>402137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>601067</t>
+          <t>655366</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>585998</t>
+          <t>638113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>614564</t>
+          <t>670000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>466842</t>
+          <t>602590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>661663</t>
+          <t>704913</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695495</t>
+          <t>722211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1443886</t>
+          <t>810247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1260212</t>
+          <t>1351245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2067857</t>
+          <t>1485075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2864890</t>
+          <t>2875473</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2797826</t>
+          <t>2825553</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2992647</t>
+          <t>2927876</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2835852</t>
+          <t>2974216</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2267052</t>
+          <t>2925276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3015443</t>
+          <t>3013312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5700741</t>
+          <t>5849689</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5102569</t>
+          <t>5780914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5910214</t>
+          <t>5914744</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
